--- a/outputs/build/diagnostics/harmonization_review.xlsx
+++ b/outputs/build/diagnostics/harmonization_review.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="near_miss" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cross_item" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="full_mapping" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="groups_now" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="original_decisions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="groups_now" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10842,7 +10843,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>camote pieces kept separate (low-confidence weight test)</t>
+          <t>bilog kept separate for this item</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -27897,6 +27898,6683 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I161"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>pull_nsu_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>original_cleaned</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>current_cleaned</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_harmonized</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>reaches_build</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>original_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>beef</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>beef</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>beef</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>intestine</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>intestine</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>intestine</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>intestine</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>drop?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2 kapinutos nga cabbage/20pesos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2 kapinutos nga cabbage/20pesos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2 kapinutos nga cabbage/20pesos</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dropped by a documented filter: ambiguous quantity</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data (2 bags of cabbage for 20 pesos) - but we can just take what's reported and get a custom weight for the PSPS respondent who had this strange unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3 for 25 pesos (putos)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 for 25 pesos (putos)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3 for 25 pesos (putos)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dropped by a documented filter: ambiguous quantity</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>half slice</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1/2 of whole</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>half of 1 unit/pieces</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>shredded cabbage(pack)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pack,shredded</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>in a pack</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pack 25 per pack in the market</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>pack 25 per pack in the market</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>pack 25 per pack in the market</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>dropped by a documented filter: not a unit</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>packs of mix vegies</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pack of mixed vegetables</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mix slice of cabbage</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>putos (halo - halo)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mixmix</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mix-mix cabbage and carrots</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sliced</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sliced</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sliced</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sliced</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>small pack for pancit (noodles)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>small pack for pancit (noodles)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>deliberate override (GENERIC_CLEAN)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cabbage</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pack of ice wrapper</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pack of ice wrapper</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>deliberate override (GENERIC_CLEAN)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>camote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>camote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>camote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>packs in cellophane</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>packs in cellophane</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>deliberate override (GENERIC_CLEAN)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>seems to have standard 1kg cellophane packs</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>camote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>camote tops</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2bond</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2bond</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2bond</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2bond</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>camote tops</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3bugkos</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3bugkos</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3bugkos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3bugkos</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>camote tops</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1bugkus</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>camote tops</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>camote tops</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>bundle</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bundle</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>bundle</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bundle</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>dropped by a documented filter: ambiguous quantity</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>putos (halo -halo )</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mixmix</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>chicken wings</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>chicken wings</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>chicken wings</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>chicken wings</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pieces of fried chicken</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>pieces of fried chicken</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>pieces of fried chicken</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>pieces of fried chicken</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sliced</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>whole chicken</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bilog nga manok</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>chicken</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>balde</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>balde</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>balde</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>balde</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>big can</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>big can</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>big can</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>big can</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>deliberate override (rename crosswalk edited)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>crackers, cookies, buiscuits, chips/curls</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fish sold per pack 90 each pack</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>putos(per pack)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>50 pesos per pinutos or plastic</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pinutos / plastic</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>pinutos / plastic</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>pinutos / plastic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>isang tumpok</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fresh fish</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>tumpok/ atado</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>yahong</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1 cone</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ice cream in cone</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>cone of an ice cream</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>gallon</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>gallon</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>gallon</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>gallons</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>deliberate override (rename crosswalk edited)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>plastic cup</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>plastic cup</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>plastic cup</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>plastic cup</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>gmay nga cup</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>maisot nga tasa</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>gamay nga tasa</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>gamay nga cup</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>gamay na tasa</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>small cup (translate)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>tub</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>tub</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>tub</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>tub</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Tupperware is size based (only 1 ob - medium sized --&gt; but smaller than medium tupperware above) --&gt; not even same province, maybe drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>tupperware medium size</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>medium tupperware is price based</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>supper ware</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>piraso</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6 bottles of redhorse</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>6 bottles of redhorse</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6 bottles of redhorse</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>dropped by a documented filter: standard quantity</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>baso</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>baso</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>baso</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>baso</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>baso = drinking glass - kept, verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>gin</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>junior</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>lipid / lapad</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>lipid / lapad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>lipid / lapad</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>lipid/lapad</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>lapad</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>lipid / lapad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>lipid / lapad</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>lipid/lapad</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, coconut wine)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>long-neck</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>long-neck</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>long-neck</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>long-neck</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>daragkul nga putos</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>dagko nga pakete</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>mabahoe nga putos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>dalagku nga putos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>large packs</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>medium nga putos</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>medium nga pakete</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>kasarangan nga putos</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>maisot nga putos</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>gagmay nga putos</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>loaf bread</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>tama-tama nga putos</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>tama-tama nga putos</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>tama-tama nga putos</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>tama-tama nga putos</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>mango</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>papaya, mango, banana</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>papaya, mango, banana</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>papaya, mango, banana</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>papaya, mango, banana</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>maybe it's a mix of these fruits?</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>mineral or spring water, all drinking water sold in containers</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>mineral or spring water, all drinking water sold in containers</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>distilled water</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>distilled water</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>distilled water</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>distilled water</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>mineral or spring water, all drinking water sold in containers</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>refilled</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>refilled</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>refilled</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>refilled</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>always 0.01 liter - the enumerators seem to know what they are on about</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>drop?</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1 serve</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>1 serve</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1 serve</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1 serve</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>drop?</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2 slice</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2 slice</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2 slice</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2 slice</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>maybe redefine qty consumed &amp; unit in psps data</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>pork</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>stick</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>stick</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>stick</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>stick</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>drop?</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrimp</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>cup</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>cup</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>cup</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>cup</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrimp</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrimp</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>pieces</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrimp</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>bilog</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>binilog</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>lata</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>lata</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>lata</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>cans</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>pakete</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>putos</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>preserved or processed meat (tocino, tapa, longaniza, etc)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>letse</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>letse</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>letse</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>letse</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sack of rice</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sack of rice</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>sack of rice</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>sack of rice</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>salmon</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>salmon</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>salmon</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>salmon</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rice</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ganta</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ganta</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ganta</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>gantang</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>rename</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>survived</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/outputs/build/diagnostics/harmonization_review.xlsx
+++ b/outputs/build/diagnostics/harmonization_review.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AH157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,40 +532,75 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>proposed_group</t>
+          <t>proposed_action</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>proposed_target</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>compared_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>fold_class</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>weight_test</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>proposed_why</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>string_only_proposed_group</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>string_only_why</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>string_only_confidence</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>prior_verdict</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>prior_verdict_from</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>verdict_landed</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Corrected Group</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -633,22 +668,53 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>loaf bread: 23@450g vs medium packs 352@450g  x1.00  ok</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>loaf bread, 23 weighings at median 450 g -- EXACTLY the medium packs median (450 g, n=352); large is 640 g and small 370 g. `tama-tama' = just right / moderate. Reading and weight agree.</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -718,24 +784,55 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>drinks at restaurant, : 189@355g vs target n=0 | loaf bread: no weighings of this spelling | pork: 11@215g vs pieces or units 15@260g  x0.83  ok | prawns, lobster, shrim: 4@15g vs pieces or units 4@15g  x1.00  ok</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>pork 215 g vs pieces or units 260 g (x1.21), inside the line. Drinks at restaurant carries 189 weighings and has NO other vocabulary, so nothing is pooled there. Prawns already fold. Loaf bread has no weighing of this spelling, so that item rests on step 1 alone.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>only candidate group, shares ['pieces']</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -803,22 +900,53 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: 21@104g vs small cup 305@100g  x1.04  ok</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ice cream, 39 weighings at 110 g. NOTE HONESTLY: the weight test does NOT support keeping this apart -- 110 g against small cup's 100 g is x1.10. The separation rests on product form, a cone being a different object from a cup, and a reviewer who weights the measurement over the form should overrule me.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -886,22 +1014,53 @@
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling | carrot: no weighings of this spelling | chicken: 2@122g vs slice 11@225g  x0.54  (not a gate: one word) | pork: 4@425g vs slice 4@425g  x1.00  (not a gate: one word)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>canonical spelling of the slice/sliced pair. Chicken shows `slice' at 122.5 g (n=2) and `sliced' at 250 g (n=9) -- reported as a note on those weighings, NOT as an objection: one word does not become two because its weighings vary.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -967,24 +1126,51 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>fresh fish: no weighings of this spelling | ice cream, sorbet, edi: no weighings of this spelling | liquor (e.g, whisky, c: no weighings of this spelling | prawns, lobster, shrim: 2@148g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2 weighings at 148 g across fresh fish, ice cream, liquor and prawns. Ice cream has a `small cup' group at 100 g, but a cup of prawns and a cup of liquor are not one object. Needs a per-item ruling.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>small cup</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>only candidate group, shares ['cup']</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1048,22 +1234,53 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: 5@1500g vs bucket 2@1065g  x1.41  ok</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>`balde' is Spanish-derived Tagalog/Visayan for bucket, and `bucket' exists in the SAME item (crackers): 1500 g (n=5) vs 1065 g (n=2), x1.41 -- inside the line.</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1127,22 +1344,53 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>beef: no weighings of this spelling | chicken: 3@935g vs patupa 3@935g  x1.00  (not a gate: one word) | fresh fish: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>canonical spelling of patupa / patupong / patopung. 3 weighings at 935 g; the other two spellings have none.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1210,22 +1458,53 @@
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: no weighings of this spelling | ice cream, sorbet, edi: 1@700g vs tupperware 5@700g  x1.00  (not a gate: one word)</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>canonical spelling of tupperware / tupper ware.</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1293,22 +1572,53 @@
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>slice</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>cabbage: 2@65g vs target n=0 | carrot: no weighings of this spelling | chicken: 9@250g vs slice 11@225g  x1.11  (not a gate: one word)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>past-participle spelling of `slice'. See the note there.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1376,22 +1686,53 @@
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>loaf bread: no weighings of this spelling | pork: 4@272g vs pieces or units 15@260g  x1.05  ok</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>pork 272.5 g (n=4) vs pieces or units 260 g (n=15), x1.05.</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1455,22 +1796,53 @@
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: 1@560g vs small cup 305@100g  x5.60</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ice cream, 720 g vs small cup 100 g. A distinct serving vessel.</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1540,24 +1912,51 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: 1@485g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ice cream, 1 weighing at 485 g, five times the small cup median. Either a large serving or a mis-weighing.</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>small cup</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>only candidate group, shares ['cup']</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1621,22 +2020,53 @@
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: 10@1000g vs small cup 305@100g  x10.00</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ice cream, 10 weighings at 1000 g, an order of magnitude above small cup and cone.</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1702,24 +2132,55 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>gallons</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: 3@950g vs gallons 5@950g  x1.00 | mineral or spring wate: 1@1000g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ice cream 975 g vs gallons 950 g is close, but `container' is also used for drinking water where it means something else. Per-item question first.</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>5-gallon blue container</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>only candidate group, shares ['container']</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1783,22 +2244,53 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: 1@750g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>`baso' is Tagalog/Visayan for drinking glass and `glass' exists in the same item (liquor). No co-occurring weighings, so this rests on the translation alone.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1866,24 +2358,55 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling | fresh fish: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>already folds to `pack'.</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>packs</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'putos'</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1947,22 +2470,53 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>cabbage: 4@275g vs pieces or units 1306@655g  x0.42</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>cabbage, 13 weighings at 275 g vs pieces or units 655 g -- about half, which is what the label says.</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2030,22 +2584,49 @@
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>beer: 2@4440g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>beer, 2 weighings at 4440 g.</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2111,24 +2692,51 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: 6@250g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>`lapad' is a flat gin bottle and `junior' is the smaller format; folding into lipid/lapad would pool two bottle sizes.</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
           <t>lipid/lapad</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>only candidate group, shares ['lapad']</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2192,22 +2800,49 @@
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>rice: 3@25000g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>rice, 3 weighings at 25 kg.</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2267,22 +2902,49 @@
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>target of the baso fold.</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2356,24 +3018,55 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling | fresh fish: 7@530g vs pack 29@620g  x0.85  (not a gate: one word)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>`per pack' is `pack' with a preposition; identity is settled by the string. Fresh fish 530 g vs pack 620 g (x0.85) is consistent but not the reason.</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>packs</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>fold key equal to a grouped label (key='pack')</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2437,22 +3130,49 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: 5@1400g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>`big' is a size qualifier and the cans group has no size strata.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2516,22 +3236,49 @@
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>mango: 4@702g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>an item list, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2595,22 +3342,49 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>mineral or spring wate: 4@1000g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>drinking water, 4 weighings at 1000 g. A refill volume, not a container.</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2676,24 +3450,55 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>chicken: 4@50g vs pieces or units 108@380g  x0.13  VETO</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>compared against the pieces group precisely so the test can speak: the ratio is what rejects the fold, not my say-so.</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>only candidate group, shares ['pieces']</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2761,22 +3566,49 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>camote tops: 4@375g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>a leading count of 2. Same class as 3bugkos and 100pcs of pandesal.</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2840,22 +3672,49 @@
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: 3@350g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>names the drink, not a unit; 3 weighings at 350 g suggests a bottle.</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2923,22 +3782,49 @@
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>pork: 2@88g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>a leading count of 2.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3002,22 +3888,49 @@
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: 2@1065g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>target of the balde fold.</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3085,22 +3998,53 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>pork: 2@1562g vs 1 order 2@1562g  x1.00  (not a gate: one word)</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>spacing variant of `1order'. `1 order' is the better spelling and should be the target; the mechanical election picks `1order' only because it is shorter.</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3164,22 +4108,49 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>chicken: 1@15g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>a cut, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3243,22 +4214,53 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>pork: 1@515g vs pieces or units 15@260g  x1.98</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>pork, 1 weighing at 515 g.</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3318,22 +4320,49 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>mineral or spring wate: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>a product type, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3397,22 +4426,53 @@
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>small packs</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>loaf bread: 1@60g vs small packs 259@370g  x0.16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>loaf bread, 60 g vs small packs 370 g. A single roll.</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3476,22 +4536,49 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>beef: 1@2060g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>a cut of meat, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3555,22 +4642,49 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>preserved or processed: 1@250g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>preserved meat, 250 g. Probably `roll', but the fold is untested.</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3634,22 +4748,53 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>pork: 1@25g vs pieces or units 15@260g  x0.10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>pork, 1 weighing at 25 g. A skewer.</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3709,22 +4854,49 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>pork: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>pork. `cooked' is a preparation state and cooked and raw weights differ, so this must NOT be folded to `bowl' without a ruling.</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3784,22 +4956,53 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrim: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>a leading count of 1 is redundant and `prawn' restates the item; the fold key reduces this to `piece'.</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3859,22 +5062,49 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>cabbage; a chopped portion. No weighings.</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3934,22 +5164,53 @@
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>caltex</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrim: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>`kabo' is a dipper; `caltex' appears alone in the same item. Both unweighed, so this rests entirely on the reading.</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4013,22 +5274,53 @@
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>1 order</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>chicken: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>run-together spelling.</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4092,22 +5384,49 @@
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>loaf bread: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>a leading count of 100.</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4171,22 +5490,49 @@
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>a leading count of 14.</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4250,22 +5596,49 @@
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>a leading count of 7.</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4325,22 +5698,53 @@
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>`apa' is the wafer cone in Visayan, and `cone' has 39 weighings in the same item. No weighing of `apa', so this rests on the translation.</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4400,22 +5804,53 @@
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>ball (tuba)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>canonical spelling of the tuba ball family: ball (tuba) / boll / bul.</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4477,24 +5912,51 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>mineral or spring wate: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>a colour qualifier distinguishing containers.</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
           <t>5-gallon blue container</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>only candidate group, shares ['gallon']</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4554,22 +6016,53 @@
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>ball (tuba)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>misspelling of `ball'; similarity 0.571, below any usable threshold, which is why it needs a hand entry.</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4633,22 +6126,49 @@
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>a leading count of 4 plus a misspelt `litre'; a volume, not an NSU.</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4708,22 +6228,49 @@
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrim: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>target of the caltex(kabo) fold.</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4783,22 +6330,53 @@
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>cans</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>`o' is `or': the label gives the English and Visayan names of one thing, and `lata' is the canonical member of the cans group.</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4860,24 +6438,51 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>camote tops: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>an item list, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>only candidate group, shares ['or']</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4937,22 +6542,49 @@
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>camote tops: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>an item, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5012,22 +6644,49 @@
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>notaunit</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>the product, not a unit.</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5091,22 +6750,53 @@
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>cone</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>reduces to `cone' once the parenthetical and the price are stripped.</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5166,22 +6856,53 @@
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>a glass or a shot; base `glass'.</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5241,22 +6962,49 @@
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>a distinct product form; `stick' alone is used for pork.</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5316,22 +7064,53 @@
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>junior lapad</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>abbreviation of `junior' in the liquor item, where `junior lapad' has 6 weighings.</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5391,22 +7170,53 @@
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>putos (mix vegetable)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>translation</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>carrot: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>a mixed-vegetable label; MIX_UNITS already covers the siblings `mix slice of cabbage' and `putos /mix mix'.</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5466,22 +7276,53 @@
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>mix vegetables (per tumpok)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>`tumbok' misspells `tumpok' (a heap). Similarity 0.947.</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5541,22 +7382,49 @@
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>carrot: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>target of the tumbok fold.</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5616,22 +7484,53 @@
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>ball (tuba)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>misspelling of `ball'.</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5691,22 +7590,53 @@
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>bugkos</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>misspelling of `bugkos' (a bundle). Cabbage here, camote tops there, so they never co-occur and no weight test is possible.</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5766,22 +7696,49 @@
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>carrot: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>a pack OF slices is a container of portions; folding to either `pack' or `slice' would lose one of the two.</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5849,24 +7806,55 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>fresh fish: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>already folds to `pack'.</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
           <t>packs</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'pack'</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5930,22 +7918,53 @@
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>pork: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>standard abbreviation of `pieces'.</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6005,22 +8024,53 @@
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>chicken: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>spelling of `patupa'.</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6080,22 +8130,53 @@
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
+          <t>patupa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>chicken: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>spelling of `patupa'.</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6159,22 +8240,53 @@
         </is>
       </c>
       <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>loaf bread: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>`per' is a preposition. Similarity to `piece' is 0.714, so no threshold would have reached this -- it needs the word, not the score.</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="AC72" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6236,24 +8348,51 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>pork: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>a barbeque stick is a distinct portion; pork already has `stick'.</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>only candidate group, shares ['pieces']</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6313,22 +8452,49 @@
       </c>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr">
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>prawns, lobster, shrim: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>bare `plastic', no weighing, in an item that also has `plastic bag' and `plastic cup'. Ambiguous between the two.</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6388,22 +8554,53 @@
       </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>bowl</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>ice cream, sorbet, edi: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>ice cream; a vessel larger than a bowl.</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6463,22 +8660,49 @@
       </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr">
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>pork: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>pork; undefined size and no weighing.</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6538,22 +8762,49 @@
       </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr">
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>loaf bread: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>distinct from `plastic cup'.</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6617,24 +8868,55 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>cabbage: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>already folds to `pack'; `supot' is a bag.</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
           <t>packs</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'putos'</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6700,24 +8982,51 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr">
         <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>carrot: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>an either/or label: sold by putos OR by pack. Not a spelling variant.</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>only candidate group, shares ['or']</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6779,24 +9088,51 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>fresh fish: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>an either/or label, with `puts' misspelling `putos'.</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
           <t>pieces or units</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>only candidate group, shares ['or']</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6862,24 +9198,55 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>small rice cooker cup</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>rice: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>one of three spellings with an IDENTICAL fold key; token-sorted similarity between all three is 1.000.</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
           <t>small cup</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>only candidate group, shares ['cup']</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6943,22 +9310,53 @@
         </is>
       </c>
       <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U82" t="inlineStr">
         <is>
+          <t>small rice cooker cup</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>rice: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>see `rice cooker cup (small)'.</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
           <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="AC82" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7018,22 +9416,49 @@
       </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>`small' is a size qualifier and no box group exists.</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
         <is>
           <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="AC83" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7097,22 +9522,49 @@
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr">
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>rice: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>target of the rice-cooker fold.</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
         <is>
           <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7172,22 +9624,49 @@
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr">
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>camote: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>camote; a size-qualified container with no group to join.</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
         <is>
           <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7247,22 +9726,49 @@
       </c>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr">
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>mineral or spring wate: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>drinking water; meaning unclear, no weighing.</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7322,22 +9828,49 @@
       </c>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr">
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>liquor (e.g, whisky, c: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>`takal' is a measure/ladle for tuba. Distinct from the ball family.</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="AC87" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7397,22 +9930,49 @@
       </c>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr">
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>chicken: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>`tingi' is retail sale in small quantities -- a selling mode rather than a fixed unit.</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
         <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="AC88" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7474,24 +10034,55 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
           <t>tumpok</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>carrot: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>already folds to `tumpok'.</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'tumpok'</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="AC89" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7555,24 +10146,55 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
           <t>tumpok</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>camote: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>already folds to `tumpok'; `(pile)' is the English gloss.</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'tumpok'</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="AC90" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7636,22 +10258,53 @@
         </is>
       </c>
       <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>fold</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
+          <t>tupperware</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>spelling</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>crackers, cookies, bui: no weighings of this spelling</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>spacing variant.</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
+        <is>
           <t>no candidate group -- may be genuinely ungrouped</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7717,24 +10370,51 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>distinct</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>carrot: 3@155g vs target n=0</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>the TARGET of the mixed-bag fold (MIX_CANON). Giving it a group would break that fold for 10 rows of other spellings.</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
           <t>packs</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>reduces to the grouped label 'putos'</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="AC92" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7798,22 +10478,33 @@
       </c>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7877,22 +10568,33 @@
       </c>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7958,24 +10660,35 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
-          <t>tumpok</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>reduces to the grouped label 'tumpok'</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>reduces to the grouped label 'tumpok'</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8039,22 +10752,33 @@
       </c>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8124,24 +10848,35 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>reduces to the grouped label 'putos'</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>reduces to the grouped label 'putos'</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8203,24 +10938,35 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>5-gallon blue container</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['blue']</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>5-gallon blue container</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['blue']</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8284,22 +11030,33 @@
       </c>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8363,22 +11120,33 @@
       </c>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8442,22 +11210,33 @@
       </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8523,24 +11302,35 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr">
         <is>
-          <t>tumpok</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['tumpok']</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>tumpok</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['tumpok']</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8610,24 +11400,35 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>reduces to the grouped label 'putos'</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>reduces to the grouped label 'putos'</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8685,24 +11486,35 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr">
         <is>
-          <t>pieces or units</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['pieces']</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['pieces']</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8770,22 +11582,33 @@
         </is>
       </c>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8845,22 +11668,33 @@
       </c>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8930,24 +11764,35 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>whole (chicken)</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['whole']</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['whole']</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9003,22 +11848,33 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9082,22 +11938,33 @@
       </c>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9157,22 +12024,33 @@
       </c>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9242,24 +12120,35 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>pieces or units</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['or']</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['or']</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9321,24 +12210,35 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr">
         <is>
-          <t>5-gallon blue container</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['gallon']</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>5-gallon blue container</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['gallon']</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9398,22 +12298,33 @@
       </c>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9473,22 +12384,33 @@
       </c>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9554,24 +12476,35 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr">
         <is>
-          <t>whole (chicken)</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['whole']</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['whole']</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9631,22 +12564,33 @@
       </c>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9702,22 +12646,33 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9779,24 +12734,35 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>bottle 500ml</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['bottle']</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>bottle 500ml</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['bottle']</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9860,22 +12826,33 @@
       </c>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9939,22 +12916,33 @@
       </c>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10018,22 +13006,33 @@
       </c>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10097,22 +13096,33 @@
       </c>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10182,24 +13192,35 @@
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>reduces to the grouped label 'putos'</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>reduces to the grouped label 'putos'</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10263,22 +13284,33 @@
       </c>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>ambiguous -- candidate groups: ['small cup', 'small packs']</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10342,22 +13374,33 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10421,22 +13464,33 @@
       </c>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10496,22 +13550,33 @@
       </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10581,24 +13646,35 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
-          <t>pieces or units</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['pieces']</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>pieces or units</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['pieces']</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10672,24 +13748,35 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>fold key equal to a grouped label (key='pack')</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>fold key equal to a grouped label (key='pack')</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10753,22 +13840,33 @@
       </c>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10832,22 +13930,33 @@
       </c>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10911,22 +14020,33 @@
       </c>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10992,24 +14112,35 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr">
         <is>
-          <t>medium packs</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['medium']</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>medium packs</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['medium']</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11073,22 +14204,33 @@
       </c>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
       <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11150,24 +14292,35 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr">
         <is>
-          <t>bottle 500ml</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['500ml']</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>bottle 500ml</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['500ml']</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11227,22 +14380,33 @@
       </c>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr"/>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11308,22 +14472,33 @@
         </is>
       </c>
       <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11391,22 +14566,33 @@
       </c>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr"/>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11470,22 +14656,33 @@
       </c>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11549,24 +14746,35 @@
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>reduces to the grouped label 'putos'</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>reduces to the grouped label 'putos'</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11626,22 +14834,33 @@
       </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr"/>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11709,24 +14928,35 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr">
         <is>
-          <t>small cup</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['cup']</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>small cup</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['cup']</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11784,24 +15014,35 @@
       <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr">
         <is>
-          <t>whole (chicken)</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['whole']</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>whole (chicken)</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['whole']</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11861,22 +15102,33 @@
       </c>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11938,24 +15190,35 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr">
         <is>
-          <t>5-gallon blue container</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['gallon']</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>5-gallon blue container</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['gallon']</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12021,22 +15284,33 @@
       </c>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr"/>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12096,22 +15370,33 @@
       </c>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12173,24 +15458,35 @@
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr">
         <is>
-          <t>gallons</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>only candidate group, shares ['gallons']</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>gallons</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>only candidate group, shares ['gallons']</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12250,22 +15546,33 @@
       </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr"/>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12321,22 +15628,33 @@
       </c>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12398,22 +15716,33 @@
       </c>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12475,22 +15804,33 @@
       </c>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>ambiguous -- candidate groups: ['large packs', 'medium packs', 'packs', 'small packs']</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12546,22 +15886,33 @@
       </c>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12633,24 +15984,35 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>fold key equal to a grouped label (key='pack')</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>fold key equal to a grouped label (key='pack')</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12712,22 +16074,33 @@
       </c>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr"/>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12789,22 +16162,33 @@
       </c>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
       <c r="AA156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12866,22 +16250,33 @@
       </c>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>no candidate group -- may be genuinely ungrouped</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>(skippable -- group governs nothing)</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>no candidate group -- may be genuinely ungrouped</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
